--- a/public/assets/templates/statistics/统计汇总-手工明细.xlsx
+++ b/public/assets/templates/statistics/统计汇总-手工明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17700"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="手工明细" sheetId="3" r:id="rId1"/>
@@ -797,27 +797,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -826,34 +826,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1380,82 +1377,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="8.88461538461539" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="11.3888888888889" customWidth="1"/>
-    <col min="2" max="2" width="10.7314814814815" customWidth="1"/>
-    <col min="3" max="3" width="20.9907407407407" customWidth="1"/>
-    <col min="5" max="5" width="17.9444444444444" customWidth="1"/>
-    <col min="7" max="7" width="16.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="13.1388888888889" customWidth="1"/>
-    <col min="18" max="18" width="17.7777777777778" customWidth="1"/>
-    <col min="19" max="19" width="22.4351851851852" customWidth="1"/>
-    <col min="20" max="20" width="28.5185185185185" customWidth="1"/>
-    <col min="21" max="21" width="12.3055555555556" customWidth="1"/>
+    <col min="1" max="1" width="11.3846153846154" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.1346153846154" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.9903846153846" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.88461538461539" style="3"/>
+    <col min="5" max="5" width="17.9423076923077" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.88461538461539" style="3"/>
+    <col min="7" max="7" width="21.1538461538462" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6923076923077" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.3461538461538" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.1442307692308" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.0961538461538" style="3" customWidth="1"/>
+    <col min="12" max="12" width="17.7788461538462" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.4326923076923" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.6346153846154" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.6634615384615" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8.88461538461539" style="3"/>
+    <col min="17" max="17" width="13.6153846153846" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="8.88461538461539" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28" customHeight="1" spans="1:23">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="40" customHeight="1" spans="1:17">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="9"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="11" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="P1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="22" customHeight="1" spans="1:23">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="2" customFormat="1" ht="22" customHeight="1" spans="1:17">
+      <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="7">
@@ -1476,53 +1475,42 @@
       <c r="G2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8" t="s">
+      <c r="I2" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8" t="s">
+      <c r="J2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
+      <c r="K2" s="11">
+        <v>536.39</v>
+      </c>
+      <c r="L2" s="11">
+        <v>482.75</v>
+      </c>
+      <c r="M2" s="11">
+        <v>261.16</v>
+      </c>
+      <c r="N2" s="11">
+        <v>109.66</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="16">
+        <v>202501</v>
+      </c>
       <c r="Q2" s="16">
-        <v>536.39</v>
-      </c>
-      <c r="R2" s="16">
-        <v>482.75</v>
-      </c>
-      <c r="S2" s="16">
-        <v>261.16</v>
-      </c>
-      <c r="T2" s="16">
-        <v>109.66</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="18">
-        <v>202501</v>
-      </c>
-      <c r="W2" s="18">
         <v>202412</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1"/>
+    <row r="3" s="2" customFormat="1"/>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A2" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="3">
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
